--- a/public/template_test.xlsx
+++ b/public/template_test.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -409,6 +409,7 @@
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -430,6 +431,9 @@
       <c r="F1" t="str">
         <v>表示スタイル</v>
       </c>
+      <c r="G1" t="str">
+        <v>画像リンク</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -525,14 +529,14 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -540,6 +544,7 @@
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -561,6 +566,9 @@
       <c r="F1" t="str">
         <v>表示スタイル</v>
       </c>
+      <c r="G1" t="str">
+        <v>画像リンク</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -648,14 +656,14 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -663,6 +671,7 @@
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -684,6 +693,9 @@
       <c r="F1" t="str">
         <v>表示スタイル</v>
       </c>
+      <c r="G1" t="str">
+        <v>画像リンク</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -806,14 +818,14 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -821,6 +833,7 @@
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -842,6 +855,9 @@
       <c r="F1" t="str">
         <v>表示スタイル</v>
       </c>
+      <c r="G1" t="str">
+        <v>画像リンク</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -969,14 +985,14 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G12"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -984,6 +1000,7 @@
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1005,6 +1022,9 @@
       <c r="F1" t="str">
         <v>表示スタイル</v>
       </c>
+      <c r="G1" t="str">
+        <v>画像リンク</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -1124,9 +1144,48 @@
         <v>box</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10">
+        <v>1990</v>
+      </c>
+      <c r="B10" t="str">
+        <v>画像付き点</v>
+      </c>
+      <c r="D10">
+        <v>12</v>
+      </c>
+      <c r="E10" t="str">
+        <v>#1565C0</v>
+      </c>
+      <c r="G10" t="str">
+        <v>https://placehold.co/96x72/1565C0/FFFFFF/png?text=1964</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>1995</v>
+      </c>
+      <c r="B11" t="str">
+        <v>【検証用】無効画像URL</v>
+      </c>
+      <c r="G11" t="str">
+        <v>not-a-url</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>2000</v>
+      </c>
+      <c r="B12" t="str">
+        <v>【検証用】data URI拒否</v>
+      </c>
+      <c r="G12" t="str">
+        <v>data:image/png;base64,AAAA</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G12"/>
   </ignoredErrors>
 </worksheet>
 </file>